--- a/db/A7XLK-4106-GroupShopping.xlsx
+++ b/db/A7XLK-4106-GroupShopping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F4E9D4-10DD-EA43-9B55-C0F05FA31773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA3A677-4B2C-C04A-A53E-7D906C6F9770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="3520" windowWidth="40000" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3520" windowWidth="40000" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shopping" sheetId="2" r:id="rId1"/>
@@ -247,6 +247,422 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
+      <t>媽媽團購好康社團，把最好的商品分享最便宜的價格給大家，希望在這個社團可以讓大家買到好用的商品。&lt;br&gt;
+本社團任何成員都能發起團購</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>請依照範例發起團購貼文。但請勿張貼任何跟團購、買賣無關之文章。請勿無故棄標。務必填上取貨方式，以便團友購買。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>因應疫情的關係, 可宅配免運送到家喔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">									&lt;ul&gt;
+										&lt;li&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>實體門市：龜山區長慶三街</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>52</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/li&gt;
+										&lt;li&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>門市電話：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>03-3288-952 &lt;/li&gt;
+										&lt;li&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>營業時間：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>10:30-20:30 &lt;/li&gt;
+										&lt;li&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>營業日：週一至週日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;/li&gt;
+										&lt;li&gt;&lt;a href="fig/A7XLK-015-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>團購</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>捌貨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-00.jpeg"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>商品列表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/a&gt;, &lt;a href="https://shop.ichefpos.com/store/OkkKDCC7/ordering"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>電子菜單</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/a&gt; &lt;/li&gt;
+										&lt;li&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>團主：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">＠最美版主 , ＠最帥小幫手 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/li&gt;
+									&lt;/ul&gt;</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>聯繫團主：＠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">978ptxwq   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>點擊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;a style="button" class="btn btn-info"  href="https://lin.ee/GyjgsRY"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>加好友</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/a&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;br&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>付款方式有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>種，現金轉帳、線上刷卡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>貨到付款超商會收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>元運費</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
       <t>捌貨專營冷凍海鮮、肉品、調理&lt;br&gt;
 商品眾多</t>
     </r>
@@ -287,7 +703,7 @@
         <charset val="136"/>
       </rPr>
       <t>！
-活動會在「記事本」公布，&lt;br&gt;
+活動會在「記事本」公布，
 商品有任何問題</t>
     </r>
     <r>
@@ -366,452 +782,7 @@
         <charset val="136"/>
       </rPr>
       <t>小盒子、
-群組內可以標記「最美版主</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>」「最帥小幫手」&lt;br&gt;
-訊息會一一回覆歐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>☺️</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>媽媽團購好康社團，把最好的商品分享最便宜的價格給大家，希望在這個社團可以讓大家買到好用的商品。&lt;br&gt;
-本社團任何成員都能發起團購</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>請依照範例發起團購貼文。但請勿張貼任何跟團購、買賣無關之文章。請勿無故棄標。務必填上取貨方式，以便團友購買。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>因應疫情的關係, 可宅配免運送到家喔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">									&lt;ul&gt;
-										&lt;li&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>實體門市：龜山區長慶三街</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>52</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>號</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;/li&gt;
-										&lt;li&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>門市電話：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>03-3288-952 &lt;/li&gt;
-										&lt;li&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>營業時間：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>10:30-20:30 &lt;/li&gt;
-										&lt;li&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>營業日：週一至週日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;/li&gt;
-										&lt;li&gt;&lt;a href="fig/A7XLK-015-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>團購</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>捌貨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-00.jpeg"&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>商品列表</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;/a&gt;, &lt;a href="https://shop.ichefpos.com/store/OkkKDCC7/ordering"&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>電子菜單</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;/a&gt; &lt;/li&gt;
-										&lt;li&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>團主：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve">＠最美版主 , ＠最帥小幫手 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;/li&gt;
-									&lt;/ul&gt;</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>聯繫團主：＠</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">978ptxwq   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>或</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>點擊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;a style="button" class="btn btn-info"  href="https://lin.ee/GyjgsRY"&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>加好友</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;/a&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;br&gt;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>付款方式有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>種，現金轉帳、線上刷卡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>貨到付款超商會收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>元運費</t>
+群組內可以標記「最美版主」「最帥小幫手」</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -820,7 +791,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -859,12 +830,6 @@
       <name val="Arial"/>
       <family val="1"/>
       <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1301,7 +1266,7 @@
         <v>99</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>17</v>
@@ -1324,13 +1289,13 @@
         <v>28</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="1">
         <v>379</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>18</v>
@@ -1353,10 +1318,10 @@
         <v>44197</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5" s="1">
         <v>2884</v>
